--- a/input/xlsx/24.xlsx
+++ b/input/xlsx/24.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="2"/>
+    <workbookView xWindow="2850" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Draft" sheetId="1" r:id="rId1"/>
     <sheet name="Play" sheetId="2" r:id="rId2"/>
     <sheet name="Results" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
-    <sheet name="Date" sheetId="5" r:id="rId5"/>
+    <sheet name="Date" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -2925,6 +2925,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -2942,24 +2962,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>